--- a/public/documents/user_templates/User_Data_Template.xlsx
+++ b/public/documents/user_templates/User_Data_Template.xlsx
@@ -1,64 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29728"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deonn Lansangan\Downloads\v1.2.3 hauoieidmo-main\public\documents\user_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72778E1A-1524-40A9-9EAA-0E5BBE6CD20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login_Info" sheetId="7" r:id="rId1"/>
+    <sheet name="Personal_Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Contact_Info" sheetId="2" r:id="rId3"/>
+    <sheet name="Prov_Contact_Info" sheetId="3" r:id="rId4"/>
+    <sheet name="Em_Contact_Info" sheetId="4" r:id="rId5"/>
+    <sheet name="Acc_Details" sheetId="5" r:id="rId6"/>
+    <sheet name="Hiring_Info" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
   <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>OFFICIAL TEMPLATE BY</t>
@@ -67,62 +57,208 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> HAU-IDMO</t>
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Reminders: </t>
+  </si>
+  <si>
     <t>Institutional Database Management Office</t>
   </si>
   <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>Dela</t>
-  </si>
-  <si>
-    <t>Cruz</t>
-  </si>
-  <si>
-    <t>HAU</t>
+    <t xml:space="preserve">&gt; Please ensure that no changes are made to the template structure. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt; Enter data only in the assigned columns. </t>
+  </si>
+  <si>
+    <t>USER RECORDS - USER RECORD UPDATE</t>
+  </si>
+  <si>
+    <t>&gt; Any modifications to the template will prevent the</t>
+  </si>
+  <si>
+    <t>Login Information</t>
+  </si>
+  <si>
+    <t>system from reading the data correctly.</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>sample@gmail.com</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Personal Information</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Middle Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Maiden Name</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Place of Birth</t>
+  </si>
+  <si>
+    <t>Civil Status</t>
+  </si>
+  <si>
+    <t>Religion</t>
+  </si>
+  <si>
+    <t>Blood Type</t>
+  </si>
+  <si>
+    <t>Records Systems and Services</t>
   </si>
   <si>
     <t>Male</t>
   </si>
   <si>
-    <t>sampleemail@hau.edu.ph</t>
-  </si>
-  <si>
-    <t>Employee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reminders: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; Please ensure that no changes are made to the template structure. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; Enter data only in the assigned columns. </t>
-  </si>
-  <si>
-    <t>&gt; Any modifications to the template will prevent the</t>
-  </si>
-  <si>
-    <t>system from reading the data correctly.</t>
-  </si>
-  <si>
-    <t>USER RECORDS - USER RECORD UPDATE</t>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Contact Information</t>
+  </si>
+  <si>
+    <t>House Number</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
+    <t>Barangay</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>Home Phone</t>
+  </si>
+  <si>
+    <t>Mobile Phone</t>
+  </si>
+  <si>
+    <t>Email Address 1</t>
+  </si>
+  <si>
+    <t>Email Address 2</t>
+  </si>
+  <si>
+    <t>sample2@gmail.com</t>
+  </si>
+  <si>
+    <t>Provincial Contact</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Emergency Information</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Accounting Details</t>
+  </si>
+  <si>
+    <t>SSS Number</t>
+  </si>
+  <si>
+    <t>Tax Identification Number</t>
+  </si>
+  <si>
+    <t>Pag IBIG Number</t>
+  </si>
+  <si>
+    <t>PhilHealth Number</t>
+  </si>
+  <si>
+    <t>Hiring Information</t>
+  </si>
+  <si>
+    <t>Date Hired</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Nature</t>
+  </si>
+  <si>
+    <t>Tenure</t>
+  </si>
+  <si>
+    <t>Non Tenured</t>
+  </si>
+  <si>
+    <t>Required License</t>
+  </si>
+  <si>
+    <t>Faculty</t>
+  </si>
+  <si>
+    <t>Full-time</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,14 +291,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="18"/>
@@ -174,6 +302,27 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -216,9 +365,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -227,25 +376,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -527,32 +690,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76D765B-9B47-4F6F-864D-2E742EEFE20A}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="15"/>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="23.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="23.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="23.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="23.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="18.75">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="B2:B4"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8" xr:uid="{CEBAF748-5EE9-4100-85CE-A6FCD49B665A}">
+      <formula1>"Employee,SuperAdmin,HR Admin,Dean,IDC Admin,ISO Document Handler"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A8" r:id="rId1" xr:uid="{394B655F-9F81-429C-A1EF-496E29AD8857}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="65.5703125" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="42.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="32.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>9</v>
+    <row r="1" spans="1:12" ht="15" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -560,15 +861,15 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1">
+      <c r="A2" s="12"/>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -576,15 +877,15 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+    <row r="3" spans="1:12" ht="23.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -592,15 +893,15 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+    <row r="4" spans="1:12" ht="23.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -608,17 +909,17 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
+    <row r="5" spans="1:12" ht="23.25">
+      <c r="A5" s="12"/>
       <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -626,11 +927,13 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
+    <row r="6" spans="1:12" ht="23.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -642,63 +945,669 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>12345</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="5" t="s">
+    <row r="7" spans="1:12" ht="18.75">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H8">
-        <v>12345</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="B7" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="C7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="8">
+        <v>54321</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="9">
+        <v>37676</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -706,10 +1615,892 @@
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C1:F2"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F498" xr:uid="{2CC27677-E14B-4892-88FD-F4E2C068D7BE}">
+      <formula1>"Male,Female"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J8:J250" xr:uid="{EC4DA00D-504B-43B4-872A-615B2A426D3F}">
+      <formula1>"Single,Married,Widowed,Separated"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L8" xr:uid="{CB9EAC1D-A911-4FD7-8709-EBA01E258842}">
+      <formula1>"A+,A-,B+,B-,O+,O-,AB+,AB-"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B5BD57D-7AE6-4F76-9833-54EA6E2059BD}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21.85546875" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1">
+      <c r="A2" s="12"/>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="23.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="23.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="23.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="23.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.75">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8">
+        <v>12345</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2009</v>
+      </c>
+      <c r="G8" s="8">
+        <v>987654321</v>
+      </c>
+      <c r="H8" s="8">
+        <v>987654321</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="K14" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="B2:B4"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1"/>
+    <hyperlink ref="I8" r:id="rId1" xr:uid="{F5A71E75-47D1-4F01-9DF0-73B84A2A0EA4}"/>
+    <hyperlink ref="J8" r:id="rId2" xr:uid="{47F30FED-6DF9-4F3D-B371-E81664C01417}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B49A8D-A6EE-4466-9104-1F8E7FD48EC6}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="59.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="15"/>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="23.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="23.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="23.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="23.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="18.75">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="8">
+        <v>12345</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2009</v>
+      </c>
+      <c r="G8" s="8">
+        <v>987654321</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="B2:B4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631417A2-3F94-413D-8C9F-DE5883DDF2FB}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="58.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="15"/>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="23.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="23.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="23.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="23.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.75">
+      <c r="A7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2009</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="8">
+        <v>2009</v>
+      </c>
+      <c r="J8" s="8">
+        <v>987654321</v>
+      </c>
+      <c r="K8" s="8">
+        <v>987654321</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="B2:B4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6938CC6A-1CF5-4A7A-B513-57A570803E03}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="12"/>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="23.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="23.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="23.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="23.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="18.75">
+      <c r="A7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="8">
+        <v>123456789</v>
+      </c>
+      <c r="B8" s="8">
+        <v>123456789</v>
+      </c>
+      <c r="C8" s="8">
+        <v>123456789</v>
+      </c>
+      <c r="D8" s="8">
+        <v>123456789</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="B2:B4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52857AB-AEB0-4FAC-8863-55C98796A1A1}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="15"/>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="23.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="23.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="23.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="23.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="18.75">
+      <c r="A7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="9">
+        <v>44981</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A6"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="B2:B4"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8:B499" xr:uid="{CF46755B-1315-4A5F-A2B4-36CA70DE7B77}">
+      <formula1>"Faculty,NTP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:C249" xr:uid="{7E05D116-A840-47C1-B549-328934A019F0}">
+      <formula1>"Full-time,Part-time"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8:D249" xr:uid="{70F5F7A8-3793-4566-B239-E84D7988D29A}">
+      <formula1>"Permanent,Probationary,Non-tenured"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F249" xr:uid="{65D84612-C937-4215-BAB5-7CADB0FAB876}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E249" xr:uid="{B4540E6F-A770-46B0-A431-3786D847CD4E}">
+      <formula1>"Fixed Term, GL, Contractual, Substitution"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>